--- a/Hoadon/HD2026/HDVao/5/001065010300_HDDienTuKhongMa.xlsx
+++ b/Hoadon/HD2026/HDVao/5/001065010300_HDDienTuKhongMa.xlsx
@@ -314,6 +314,573 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>K26TAA</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>42601</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>0300792451-009</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH CÔNG TY TRÁCH NHIỆM HỮU HẠN NƯỚC GIẢI KHÁT COCA-COLA VIỆT NAM TẠI TỈNH TÂY NINH</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>001065010300</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>CỬA HÀNG BIA- NƯỚC NGỌT HÙNG MẠNH</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>SỐ 18/6 ẤP PHƯỚC BÌNH, XÃ PHƯỚC TỈNH - HUYỆN LONG ĐIỀN, TỈNH BÀ RỊA VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="L7" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>K26TAA</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>42602</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>0300792451-009</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH CÔNG TY TRÁCH NHIỆM HỮU HẠN NƯỚC GIẢI KHÁT COCA-COLA VIỆT NAM TẠI TỈNH TÂY NINH</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>001065010300</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>CỬA HÀNG BIA- NƯỚC NGỌT HÙNG MẠNH</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>SỐ 18/6 ẤP PHƯỚC BÌNH, XÃ PHƯỚC TỈNH - HUYỆN LONG ĐIỀN, TỈNH BÀ RỊA VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="L8" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S8" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>K26TAA</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>42610</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>0300792451-009</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH CÔNG TY TRÁCH NHIỆM HỮU HẠN NƯỚC GIẢI KHÁT COCA-COLA VIỆT NAM TẠI TỈNH TÂY NINH</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>001065010300</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>CỬA HÀNG BIA- NƯỚC NGỌT HÙNG MẠNH</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>SỐ 18/6 ẤP PHƯỚC BÌNH, XÃ PHƯỚC TỈNH - HUYỆN LONG ĐIỀN, TỈNH BÀ RỊA VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="n">
+        <v>5524940.0</v>
+      </c>
+      <c r="L9" s="13" t="n">
+        <v>477268.0</v>
+      </c>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13" t="n">
+        <v>6002208.0</v>
+      </c>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q9" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S9" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>K26TAA</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>43834</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>0300792451-009</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH CÔNG TY TRÁCH NHIỆM HỮU HẠN NƯỚC GIẢI KHÁT COCA-COLA VIỆT NAM TẠI TỈNH TÂY NINH</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>001065010300</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>CỬA HÀNG BIA- NƯỚC NGỌT HÙNG MẠNH</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>SỐ 18/6 ẤP PHƯỚC BÌNH, XÃ PHƯỚC TỈNH - HUYỆN LONG ĐIỀN, TỈNH BÀ RỊA VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="L10" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S10" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>K26TAA</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>43845</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>0300792451-009</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH CÔNG TY TRÁCH NHIỆM HỮU HẠN NƯỚC GIẢI KHÁT COCA-COLA VIỆT NAM TẠI TỈNH TÂY NINH</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>001065010300</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>CỬA HÀNG BIA- NƯỚC NGỌT HÙNG MẠNH</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>SỐ 18/6 ẤP PHƯỚC BÌNH, XÃ PHƯỚC TỈNH - HUYỆN LONG ĐIỀN, TỈNH BÀ RỊA VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="n">
+        <v>3134600.0</v>
+      </c>
+      <c r="L11" s="13" t="n">
+        <v>298223.0</v>
+      </c>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13" t="n">
+        <v>3432823.0</v>
+      </c>
+      <c r="P11" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q11" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S11" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>K26TAA</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>44210</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>0300792451-009</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH CÔNG TY TRÁCH NHIỆM HỮU HẠN NƯỚC GIẢI KHÁT COCA-COLA VIỆT NAM TẠI TỈNH TÂY NINH</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>001065010300</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>CỬA HÀNG BIA- NƯỚC NGỌT HÙNG MẠNH</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>SỐ 18/6 ẤP PHƯỚC BÌNH, XÃ PHƯỚC TỈNH - HUYỆN LONG ĐIỀN, TỈNH BÀ RỊA VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="L12" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>K26TAA</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>44216</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>0300792451-009</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH CÔNG TY TRÁCH NHIỆM HỮU HẠN NƯỚC GIẢI KHÁT COCA-COLA VIỆT NAM TẠI TỈNH TÂY NINH</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>001065010300</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>CỬA HÀNG BIA- NƯỚC NGỌT HÙNG MẠNH</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>SỐ 18/6 ẤP PHƯỚC BÌNH, XÃ PHƯỚC TỈNH - HUYỆN LONG ĐIỀN, TỈNH BÀ RỊA VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>4129640.0</v>
+      </c>
+      <c r="L13" s="13" t="n">
+        <v>400917.0</v>
+      </c>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13" t="n">
+        <v>4530557.0</v>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>Tổng cục thuế đã nhận không mã</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:S3"/>
